--- a/application/views/rpt/ru/LedgerPayments.xlsx
+++ b/application/views/rpt/ru/LedgerPayments.xlsx
@@ -5,21 +5,21 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\iSell\www\isell\application\views\rpt\ru\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Wamp.NET\sites\isell\isell\application\views\rpt\ru\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508"/>
   </bookViews>
   <sheets>
     <sheet name="Акт звіряння" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>Документ</t>
   </si>
@@ -160,6 +160,12 @@
   </si>
   <si>
     <t>Мы, нижеподписавшиеся, представитель предприятия {$v-&gt;a-&gt;company_name} в лице гл.бухгалтера {$v-&gt;accountant_name} с одной стороны и представитель предприятия {$v-&gt;p-&gt;company_name} в лице гл.бухгалтера    с другой стороны, подписали настоящий Акт сверки взаимных расчетов по состоянию на  {$v-&gt;flocalDate} г. о нижеследующем:</t>
+  </si>
+  <si>
+    <t>{$v-&gt;ledger-&gt;rows[]-&gt;row_total}</t>
+  </si>
+  <si>
+    <t>Остаток</t>
   </si>
 </sst>
 </file>
@@ -247,7 +253,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -301,13 +307,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -325,7 +331,7 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -334,52 +340,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -394,7 +355,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -411,32 +372,63 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -449,45 +441,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -798,125 +751,112 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="44.7109375" style="1" customWidth="1"/>
-    <col min="4" max="7" width="12.28515625" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="3.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" style="1" customWidth="1"/>
+    <col min="4" max="6" width="12.33203125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-    </row>
-    <row r="2" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+    </row>
+    <row r="2" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="33" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-    </row>
-    <row r="4" spans="1:7" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="35" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+    </row>
+    <row r="4" spans="1:6" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-    </row>
-    <row r="5" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+    </row>
+    <row r="5" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27" t="s">
+      <c r="E5" s="22"/>
+      <c r="F5" s="15"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="21"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <v>1</v>
+      </c>
+      <c r="B7" s="11">
+        <v>2</v>
+      </c>
+      <c r="C7" s="11">
+        <v>3</v>
+      </c>
+      <c r="D7" s="11">
+        <v>4</v>
+      </c>
+      <c r="E7" s="11">
         <v>5</v>
       </c>
-      <c r="G5" s="28"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="31"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="15">
-        <v>1</v>
-      </c>
-      <c r="B7" s="13">
-        <v>2</v>
-      </c>
-      <c r="C7" s="13">
-        <v>3</v>
-      </c>
-      <c r="D7" s="13">
-        <v>4</v>
-      </c>
-      <c r="E7" s="13">
-        <v>5</v>
-      </c>
-      <c r="F7" s="13">
+      <c r="F7" s="11">
         <v>6</v>
       </c>
-      <c r="G7" s="14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="7" t="s">
         <v>27</v>
       </c>
@@ -924,10 +864,9 @@
         <v>28</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="8"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -942,188 +881,175 @@
       <c r="E9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="8"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="25" t="s">
+      <c r="F9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="16" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="13" t="s">
         <v>12</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="23" t="s">
+    </row>
+    <row r="11" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="10" t="s">
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
-    </row>
-    <row r="12" spans="1:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:6" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19" t="s">
+    </row>
+    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="19" t="s">
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+    </row>
+    <row r="14" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="21" t="s">
+      <c r="B14" s="28"/>
+      <c r="C14" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="19" t="s">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-    </row>
-    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22" t="s">
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-    </row>
-    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19" t="s">
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19" t="s">
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20" t="s">
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A4:G4"/>
+  <mergeCells count="23">
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D18:G18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="77" orientation="portrait" r:id="rId1"/>
